--- a/Excel/STUDI KASUS.xlsx
+++ b/Excel/STUDI KASUS.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B3AD1D-0788-485A-9687-08BDAFBB01A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="691" activeTab="1" xr2:uid="{901D0503-6946-40CA-8D36-37B156763246}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="691" activeTab="3" xr2:uid="{901D0503-6946-40CA-8D36-37B156763246}"/>
   </bookViews>
   <sheets>
     <sheet name="Kost" sheetId="3" r:id="rId1"/>

--- a/Excel/STUDI KASUS.xlsx
+++ b/Excel/STUDI KASUS.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UNDIPA\Semester 7\Skripsi\skripsi\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KULIAH\SEMESTER 7\PROPOSAL SKRIPSI\skripsi\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B3AD1D-0788-485A-9687-08BDAFBB01A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C85728-27EE-4038-B521-314B4788FF5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="691" activeTab="3" xr2:uid="{901D0503-6946-40CA-8D36-37B156763246}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="691" activeTab="3" xr2:uid="{901D0503-6946-40CA-8D36-37B156763246}"/>
   </bookViews>
   <sheets>
     <sheet name="Kost" sheetId="3" r:id="rId1"/>
@@ -1844,7 +1844,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="105">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -2120,6 +2120,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3105,26 +3108,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E46AEE5-C1DF-4E3B-B1A0-CC373A6F6C73}">
   <dimension ref="A2:P49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="4.44140625" customWidth="1"/>
-    <col min="3" max="3" width="28.21875" customWidth="1"/>
-    <col min="4" max="4" width="17.33203125" customWidth="1"/>
-    <col min="5" max="5" width="25.109375" customWidth="1"/>
-    <col min="6" max="6" width="18.33203125" customWidth="1"/>
-    <col min="7" max="7" width="12.5546875" customWidth="1"/>
+    <col min="1" max="2" width="4.453125" customWidth="1"/>
+    <col min="3" max="3" width="28.1796875" customWidth="1"/>
+    <col min="4" max="4" width="17.36328125" customWidth="1"/>
+    <col min="5" max="5" width="25.08984375" customWidth="1"/>
+    <col min="6" max="6" width="18.36328125" customWidth="1"/>
+    <col min="7" max="7" width="12.54296875" customWidth="1"/>
     <col min="8" max="8" width="29" customWidth="1"/>
-    <col min="9" max="9" width="16.109375" customWidth="1"/>
-    <col min="10" max="10" width="13.77734375" customWidth="1"/>
-    <col min="11" max="11" width="18.109375" customWidth="1"/>
-    <col min="12" max="12" width="13.44140625" customWidth="1"/>
-    <col min="13" max="13" width="11.44140625" customWidth="1"/>
-    <col min="14" max="14" width="18.88671875" customWidth="1"/>
-    <col min="15" max="15" width="20.6640625" customWidth="1"/>
-    <col min="16" max="16" width="18.21875" customWidth="1"/>
+    <col min="9" max="9" width="16.08984375" customWidth="1"/>
+    <col min="10" max="10" width="13.81640625" customWidth="1"/>
+    <col min="11" max="11" width="18.08984375" customWidth="1"/>
+    <col min="12" max="12" width="13.453125" customWidth="1"/>
+    <col min="13" max="13" width="11.453125" customWidth="1"/>
+    <col min="14" max="14" width="18.90625" customWidth="1"/>
+    <col min="15" max="15" width="20.6328125" customWidth="1"/>
+    <col min="16" max="16" width="18.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>44</v>
       </c>
@@ -3174,7 +3177,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A3" s="6">
         <v>1</v>
       </c>
@@ -3221,7 +3224,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="116" x14ac:dyDescent="0.35">
       <c r="A4" s="6">
         <v>2</v>
       </c>
@@ -3268,7 +3271,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="115.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="116" x14ac:dyDescent="0.35">
       <c r="A5" s="9">
         <v>3</v>
       </c>
@@ -3315,7 +3318,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
         <v>4</v>
       </c>
@@ -3365,7 +3368,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
         <v>5</v>
       </c>
@@ -3415,7 +3418,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="87" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <v>6</v>
       </c>
@@ -3465,7 +3468,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <v>7</v>
       </c>
@@ -3515,7 +3518,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
         <v>8</v>
       </c>
@@ -3561,7 +3564,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
         <v>9</v>
       </c>
@@ -3611,7 +3614,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
         <v>10</v>
       </c>
@@ -3661,7 +3664,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <v>11</v>
       </c>
@@ -3705,7 +3708,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A14" s="9">
         <v>12</v>
       </c>
@@ -3749,7 +3752,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
         <v>13</v>
       </c>
@@ -3793,7 +3796,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <v>14</v>
       </c>
@@ -3837,7 +3840,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="58" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
         <v>15</v>
       </c>
@@ -3881,7 +3884,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A18" s="9">
         <v>16</v>
       </c>
@@ -3925,111 +3928,111 @@
         <v>395</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B19" s="9"/>
       <c r="F19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="3"/>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B20" s="9"/>
       <c r="F20" s="2"/>
       <c r="H20" s="2"/>
       <c r="I20" s="3"/>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B21" s="9"/>
       <c r="F21" s="2"/>
       <c r="I21" s="3"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B22" s="9"/>
       <c r="F22" s="2"/>
       <c r="I22" s="3"/>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B23" s="9"/>
       <c r="F23" s="2"/>
       <c r="N23" s="25"/>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B24" s="9"/>
       <c r="F24" s="2"/>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B25" s="9"/>
       <c r="F25" s="2"/>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B26" s="9"/>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B27" s="9"/>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B28" s="9"/>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B29" s="9"/>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B30" s="9"/>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B31" s="9"/>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="B32" s="9"/>
     </row>
-    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B33" s="9"/>
     </row>
-    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B34" s="9"/>
     </row>
-    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B35" s="9"/>
     </row>
-    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B36" s="9"/>
     </row>
-    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B37" s="9"/>
     </row>
-    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B38" s="9"/>
     </row>
-    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B39" s="9"/>
     </row>
-    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B40" s="9"/>
     </row>
-    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B41" s="9"/>
     </row>
-    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B42" s="9"/>
     </row>
-    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B43" s="9"/>
     </row>
-    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B44" s="9"/>
     </row>
-    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B45" s="9"/>
     </row>
-    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B46" s="9"/>
     </row>
-    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B47" s="9"/>
     </row>
-    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B48" s="9"/>
     </row>
-    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B49" s="9"/>
     </row>
   </sheetData>
@@ -4041,27 +4044,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{015FA8AF-97B1-4BAE-BA56-FF4AAB7B8C3B}">
   <dimension ref="A1:P27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" customWidth="1"/>
-    <col min="2" max="2" width="19.21875" customWidth="1"/>
-    <col min="3" max="3" width="16.109375" customWidth="1"/>
-    <col min="4" max="4" width="24.6640625" customWidth="1"/>
+    <col min="1" max="1" width="10.36328125" customWidth="1"/>
+    <col min="2" max="2" width="19.1796875" customWidth="1"/>
+    <col min="3" max="3" width="16.08984375" customWidth="1"/>
+    <col min="4" max="4" width="24.6328125" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="13.5546875" customWidth="1"/>
-    <col min="7" max="7" width="14.21875" customWidth="1"/>
-    <col min="8" max="8" width="16.21875" customWidth="1"/>
-    <col min="9" max="9" width="23.6640625" customWidth="1"/>
-    <col min="10" max="10" width="14.6640625" customWidth="1"/>
-    <col min="11" max="11" width="21.88671875" customWidth="1"/>
-    <col min="12" max="12" width="27.44140625" customWidth="1"/>
-    <col min="13" max="13" width="20.21875" customWidth="1"/>
-    <col min="14" max="14" width="22.6640625" customWidth="1"/>
-    <col min="15" max="15" width="16.21875" customWidth="1"/>
-    <col min="16" max="16" width="15.109375" customWidth="1"/>
+    <col min="6" max="6" width="13.54296875" customWidth="1"/>
+    <col min="7" max="7" width="14.1796875" customWidth="1"/>
+    <col min="8" max="8" width="16.1796875" customWidth="1"/>
+    <col min="9" max="9" width="23.6328125" customWidth="1"/>
+    <col min="10" max="10" width="14.6328125" customWidth="1"/>
+    <col min="11" max="11" width="21.90625" customWidth="1"/>
+    <col min="12" max="12" width="27.453125" customWidth="1"/>
+    <col min="13" max="13" width="20.1796875" customWidth="1"/>
+    <col min="14" max="14" width="22.6328125" customWidth="1"/>
+    <col min="15" max="15" width="16.1796875" customWidth="1"/>
+    <col min="16" max="16" width="15.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
         <v>109</v>
       </c>
@@ -4111,7 +4114,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A2" s="12" t="s">
         <v>127</v>
       </c>
@@ -4161,7 +4164,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="72" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A3" s="12" t="s">
         <v>128</v>
       </c>
@@ -4211,7 +4214,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="12" t="s">
         <v>129</v>
       </c>
@@ -4261,7 +4264,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A5" s="12" t="s">
         <v>176</v>
       </c>
@@ -4311,7 +4314,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="12" t="s">
         <v>182</v>
       </c>
@@ -4361,7 +4364,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" s="12" t="s">
         <v>187</v>
       </c>
@@ -4411,7 +4414,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A8" s="12" t="s">
         <v>285</v>
       </c>
@@ -4461,7 +4464,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A9" s="12" t="s">
         <v>288</v>
       </c>
@@ -4511,7 +4514,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A10" s="12" t="s">
         <v>290</v>
       </c>
@@ -4561,7 +4564,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A11" s="12" t="s">
         <v>291</v>
       </c>
@@ -4611,7 +4614,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A12" s="12" t="s">
         <v>420</v>
       </c>
@@ -4661,7 +4664,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A13" s="12" t="s">
         <v>421</v>
       </c>
@@ -4711,7 +4714,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" s="12" t="s">
         <v>422</v>
       </c>
@@ -4761,7 +4764,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A15" s="12" t="s">
         <v>423</v>
       </c>
@@ -4811,7 +4814,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" ht="58" x14ac:dyDescent="0.35">
       <c r="A16" s="12" t="s">
         <v>424</v>
       </c>
@@ -4861,7 +4864,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="12" t="s">
         <v>425</v>
       </c>
@@ -4911,7 +4914,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>340</v>
       </c>
@@ -4941,25 +4944,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69BA1C62-8752-4999-BB16-F79297149C3E}">
   <dimension ref="A1:AB189"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.77734375" customWidth="1"/>
-    <col min="3" max="4" width="10.21875" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="19.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" customWidth="1"/>
+    <col min="3" max="4" width="10.1796875" customWidth="1"/>
+    <col min="5" max="5" width="20.453125" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.44140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
-    <col min="9" max="9" width="11.109375" customWidth="1"/>
-    <col min="10" max="10" width="14.44140625" customWidth="1"/>
-    <col min="11" max="11" width="15.77734375" customWidth="1"/>
+    <col min="7" max="7" width="27.453125" customWidth="1"/>
+    <col min="8" max="8" width="10.54296875" customWidth="1"/>
+    <col min="9" max="9" width="11.08984375" customWidth="1"/>
+    <col min="10" max="10" width="14.453125" customWidth="1"/>
+    <col min="11" max="11" width="15.81640625" customWidth="1"/>
     <col min="12" max="12" width="13" customWidth="1"/>
-    <col min="13" max="13" width="11.44140625" customWidth="1"/>
-    <col min="15" max="15" width="20.21875" customWidth="1"/>
-    <col min="19" max="19" width="17.44140625" customWidth="1"/>
+    <col min="13" max="13" width="11.453125" customWidth="1"/>
+    <col min="15" max="15" width="20.1796875" customWidth="1"/>
+    <col min="19" max="19" width="17.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>111</v>
       </c>
@@ -4967,7 +4970,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="9" t="s">
         <v>112</v>
       </c>
@@ -4975,7 +4978,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="9" t="s">
         <v>17</v>
       </c>
@@ -5001,7 +5004,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="9" t="s">
         <v>18</v>
       </c>
@@ -5027,7 +5030,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
         <v>19</v>
       </c>
@@ -5053,7 +5056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:16" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
         <v>20</v>
       </c>
@@ -5079,7 +5082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:16" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="9" t="s">
         <v>21</v>
       </c>
@@ -5099,7 +5102,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="9" t="s">
         <v>22</v>
       </c>
@@ -5119,7 +5122,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="9" t="s">
         <v>23</v>
       </c>
@@ -5139,7 +5142,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="9" t="s">
         <v>24</v>
       </c>
@@ -5147,7 +5150,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="9" t="s">
         <v>25</v>
       </c>
@@ -5173,7 +5176,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="9"/>
       <c r="B12" s="17"/>
       <c r="G12" t="s">
@@ -5195,7 +5198,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="15"/>
       <c r="G13" t="s">
         <v>105</v>
@@ -5216,7 +5219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B14" s="15"/>
       <c r="G14" t="s">
         <v>372</v>
@@ -5237,7 +5240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A15" s="18" t="s">
         <v>110</v>
       </c>
@@ -5255,7 +5258,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A16" s="9"/>
       <c r="B16" s="15"/>
       <c r="G16" t="s">
@@ -5265,7 +5268,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
         <v>112</v>
       </c>
@@ -5284,7 +5287,7 @@
       </c>
       <c r="K17" s="3"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>17</v>
       </c>
@@ -5307,7 +5310,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>18</v>
       </c>
@@ -5330,7 +5333,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>19</v>
       </c>
@@ -5353,7 +5356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>20</v>
       </c>
@@ -5388,7 +5391,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
         <v>21</v>
       </c>
@@ -5423,7 +5426,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
         <v>22</v>
       </c>
@@ -5452,7 +5455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
         <v>23</v>
       </c>
@@ -5481,7 +5484,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
         <v>24</v>
       </c>
@@ -5510,7 +5513,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
         <v>25</v>
       </c>
@@ -5539,7 +5542,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A27" s="9"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15">
@@ -5567,7 +5570,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="42" t="s">
@@ -5580,12 +5583,12 @@
         <v>478</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A30" s="18" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="15" t="s">
         <v>112</v>
       </c>
@@ -5593,7 +5596,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="9" t="s">
         <v>17</v>
       </c>
@@ -5601,7 +5604,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="9" t="s">
         <v>18</v>
       </c>
@@ -5612,7 +5615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="9" t="s">
         <v>19</v>
       </c>
@@ -5623,7 +5626,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="9" t="s">
         <v>20</v>
       </c>
@@ -5634,7 +5637,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="9" t="s">
         <v>21</v>
       </c>
@@ -5645,7 +5648,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="9" t="s">
         <v>22</v>
       </c>
@@ -5656,7 +5659,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="9" t="s">
         <v>23</v>
       </c>
@@ -5667,7 +5670,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="9" t="s">
         <v>24</v>
       </c>
@@ -5678,7 +5681,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="9" t="s">
         <v>25</v>
       </c>
@@ -5689,32 +5692,32 @@
         <v>151</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="E42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" x14ac:dyDescent="0.35">
       <c r="E43" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" x14ac:dyDescent="0.35">
       <c r="E44" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="46" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="18"/>
     </row>
-    <row r="48" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="33" t="s">
         <v>109</v>
       </c>
@@ -5751,7 +5754,7 @@
       <c r="L48" s="16"/>
       <c r="M48" s="16"/>
     </row>
-    <row r="49" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="35" t="s">
         <v>127</v>
       </c>
@@ -5788,7 +5791,7 @@
       <c r="L49" s="12"/>
       <c r="M49" s="12"/>
     </row>
-    <row r="50" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="35" t="s">
         <v>128</v>
       </c>
@@ -5825,7 +5828,7 @@
       <c r="L50" s="12"/>
       <c r="M50" s="12"/>
     </row>
-    <row r="51" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="35" t="s">
         <v>129</v>
       </c>
@@ -5862,7 +5865,7 @@
       <c r="L51" s="12"/>
       <c r="M51" s="12"/>
     </row>
-    <row r="52" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="35" t="s">
         <v>176</v>
       </c>
@@ -5897,7 +5900,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="35" t="s">
         <v>182</v>
       </c>
@@ -5932,7 +5935,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="35" t="s">
         <v>187</v>
       </c>
@@ -5967,7 +5970,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="55" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="35" t="s">
         <v>285</v>
       </c>
@@ -6002,7 +6005,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="56" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="35" t="s">
         <v>288</v>
       </c>
@@ -6039,7 +6042,7 @@
       <c r="L56" s="9"/>
       <c r="M56" s="9"/>
     </row>
-    <row r="57" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="35" t="s">
         <v>290</v>
       </c>
@@ -6076,7 +6079,7 @@
       <c r="L57" s="12"/>
       <c r="M57" s="12"/>
     </row>
-    <row r="58" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="35" t="s">
         <v>291</v>
       </c>
@@ -6113,7 +6116,7 @@
       <c r="L58" s="12"/>
       <c r="M58" s="12"/>
     </row>
-    <row r="59" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="35" t="s">
         <v>420</v>
       </c>
@@ -6150,7 +6153,7 @@
       <c r="L59" s="12"/>
       <c r="M59" s="12"/>
     </row>
-    <row r="60" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="35" t="s">
         <v>421</v>
       </c>
@@ -6187,7 +6190,7 @@
       <c r="L60" s="12"/>
       <c r="M60" s="12"/>
     </row>
-    <row r="61" spans="1:13" ht="21" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="35" t="s">
         <v>422</v>
       </c>
@@ -6224,7 +6227,7 @@
       <c r="L61" s="12"/>
       <c r="M61" s="12"/>
     </row>
-    <row r="62" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="35" t="s">
         <v>423</v>
       </c>
@@ -6261,7 +6264,7 @@
       <c r="L62" s="12"/>
       <c r="M62" s="12"/>
     </row>
-    <row r="63" spans="1:13" ht="21" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="35" t="s">
         <v>424</v>
       </c>
@@ -6298,7 +6301,7 @@
       <c r="L63" s="12"/>
       <c r="M63" s="12"/>
     </row>
-    <row r="64" spans="1:13" ht="21" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:13" ht="21.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="35" t="s">
         <v>425</v>
       </c>
@@ -6335,13 +6338,13 @@
       <c r="L64" s="12"/>
       <c r="M64" s="12"/>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A66" s="37" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="68" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="68" spans="1:12" ht="15.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="38" t="s">
         <v>138</v>
       </c>
@@ -6373,7 +6376,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="40" t="s">
         <v>127</v>
       </c>
@@ -6405,7 +6408,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="40" t="s">
         <v>128</v>
       </c>
@@ -6438,7 +6441,7 @@
       </c>
       <c r="L70" s="9"/>
     </row>
-    <row r="71" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="40" t="s">
         <v>129</v>
       </c>
@@ -6471,7 +6474,7 @@
       </c>
       <c r="L71" s="9"/>
     </row>
-    <row r="72" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="40" t="s">
         <v>176</v>
       </c>
@@ -6505,7 +6508,7 @@
       <c r="K72" s="9"/>
       <c r="L72" s="9"/>
     </row>
-    <row r="73" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="40" t="s">
         <v>182</v>
       </c>
@@ -6539,7 +6542,7 @@
       <c r="K73" s="9"/>
       <c r="L73" s="9"/>
     </row>
-    <row r="74" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="40" t="s">
         <v>187</v>
       </c>
@@ -6573,7 +6576,7 @@
       <c r="K74" s="9"/>
       <c r="L74" s="9"/>
     </row>
-    <row r="75" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="40" t="s">
         <v>285</v>
       </c>
@@ -6607,7 +6610,7 @@
       <c r="K75" s="9"/>
       <c r="L75" s="9"/>
     </row>
-    <row r="76" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="40" t="s">
         <v>288</v>
       </c>
@@ -6641,7 +6644,7 @@
       <c r="K76" s="9"/>
       <c r="L76" s="9"/>
     </row>
-    <row r="77" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="40" t="s">
         <v>290</v>
       </c>
@@ -6675,7 +6678,7 @@
       <c r="K77" s="9"/>
       <c r="L77" s="9"/>
     </row>
-    <row r="78" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="40" t="s">
         <v>291</v>
       </c>
@@ -6709,7 +6712,7 @@
       <c r="K78" s="9"/>
       <c r="L78" s="9"/>
     </row>
-    <row r="79" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="40" t="s">
         <v>420</v>
       </c>
@@ -6743,7 +6746,7 @@
       <c r="K79" s="9"/>
       <c r="L79" s="9"/>
     </row>
-    <row r="80" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="40" t="s">
         <v>421</v>
       </c>
@@ -6777,7 +6780,7 @@
       <c r="K80" s="9"/>
       <c r="L80" s="9"/>
     </row>
-    <row r="81" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="40" t="s">
         <v>422</v>
       </c>
@@ -6811,7 +6814,7 @@
       <c r="K81" s="9"/>
       <c r="L81" s="9"/>
     </row>
-    <row r="82" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="40" t="s">
         <v>423</v>
       </c>
@@ -6845,7 +6848,7 @@
       <c r="K82" s="9"/>
       <c r="L82" s="9"/>
     </row>
-    <row r="83" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="40" t="s">
         <v>424</v>
       </c>
@@ -6879,7 +6882,7 @@
       <c r="K83" s="9"/>
       <c r="L83" s="9"/>
     </row>
-    <row r="84" spans="1:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:12" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="40" t="s">
         <v>425</v>
       </c>
@@ -6913,12 +6916,12 @@
       <c r="K84" s="9"/>
       <c r="L84" s="9"/>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A86" s="18" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>140</v>
       </c>
@@ -6929,7 +6932,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>127</v>
       </c>
@@ -6952,7 +6955,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>128</v>
       </c>
@@ -6975,7 +6978,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>129</v>
       </c>
@@ -6998,7 +7001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>176</v>
       </c>
@@ -7021,7 +7024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>182</v>
       </c>
@@ -7044,7 +7047,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>187</v>
       </c>
@@ -7067,7 +7070,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>285</v>
       </c>
@@ -7090,7 +7093,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>288</v>
       </c>
@@ -7113,7 +7116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>290</v>
       </c>
@@ -7136,7 +7139,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>291</v>
       </c>
@@ -7159,7 +7162,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>420</v>
       </c>
@@ -7182,7 +7185,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>421</v>
       </c>
@@ -7205,7 +7208,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>422</v>
       </c>
@@ -7228,7 +7231,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>423</v>
       </c>
@@ -7251,7 +7254,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>424</v>
       </c>
@@ -7274,7 +7277,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>425</v>
       </c>
@@ -7297,7 +7300,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>223</v>
       </c>
@@ -7308,7 +7311,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>127</v>
       </c>
@@ -7331,7 +7334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>128</v>
       </c>
@@ -7354,7 +7357,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>129</v>
       </c>
@@ -7377,7 +7380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>176</v>
       </c>
@@ -7400,7 +7403,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>182</v>
       </c>
@@ -7423,7 +7426,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>187</v>
       </c>
@@ -7446,7 +7449,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>285</v>
       </c>
@@ -7469,7 +7472,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>288</v>
       </c>
@@ -7492,7 +7495,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>290</v>
       </c>
@@ -7515,7 +7518,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>291</v>
       </c>
@@ -7538,7 +7541,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>420</v>
       </c>
@@ -7561,7 +7564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>421</v>
       </c>
@@ -7584,7 +7587,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>422</v>
       </c>
@@ -7607,7 +7610,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>423</v>
       </c>
@@ -7630,7 +7633,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>424</v>
       </c>
@@ -7653,7 +7656,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>425</v>
       </c>
@@ -7676,7 +7679,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>145</v>
       </c>
@@ -7687,7 +7690,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>127</v>
       </c>
@@ -7710,7 +7713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>128</v>
       </c>
@@ -7733,7 +7736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>129</v>
       </c>
@@ -7756,7 +7759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>176</v>
       </c>
@@ -7779,7 +7782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>182</v>
       </c>
@@ -7802,7 +7805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>187</v>
       </c>
@@ -7825,7 +7828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>285</v>
       </c>
@@ -7848,7 +7851,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="133" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>288</v>
       </c>
@@ -7871,7 +7874,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="134" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>290</v>
       </c>
@@ -7894,7 +7897,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="135" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>291</v>
       </c>
@@ -7917,7 +7920,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="136" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>420</v>
       </c>
@@ -7940,7 +7943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>421</v>
       </c>
@@ -7963,7 +7966,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="138" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>422</v>
       </c>
@@ -7986,7 +7989,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="139" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>423</v>
       </c>
@@ -8009,7 +8012,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="140" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>424</v>
       </c>
@@ -8032,7 +8035,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>425</v>
       </c>
@@ -8055,12 +8058,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A145" s="9" t="s">
         <v>138</v>
       </c>
@@ -8123,7 +8126,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A146" s="9" t="s">
         <v>127</v>
       </c>
@@ -8195,7 +8198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A147" s="9" t="s">
         <v>128</v>
       </c>
@@ -8267,7 +8270,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A148" s="9" t="s">
         <v>129</v>
       </c>
@@ -8339,7 +8342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A149" s="9" t="s">
         <v>176</v>
       </c>
@@ -8411,7 +8414,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A150" s="9" t="s">
         <v>182</v>
       </c>
@@ -8483,7 +8486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A151" s="9" t="s">
         <v>187</v>
       </c>
@@ -8555,7 +8558,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A152" s="9" t="s">
         <v>285</v>
       </c>
@@ -8627,7 +8630,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A153" s="9" t="s">
         <v>288</v>
       </c>
@@ -8699,7 +8702,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A154" s="9" t="s">
         <v>290</v>
       </c>
@@ -8771,7 +8774,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A155" s="9" t="s">
         <v>291</v>
       </c>
@@ -8842,7 +8845,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A156" s="9" t="s">
         <v>420</v>
       </c>
@@ -8913,7 +8916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A157" s="9" t="s">
         <v>421</v>
       </c>
@@ -8984,7 +8987,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A158" s="9" t="s">
         <v>422</v>
       </c>
@@ -9055,7 +9058,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A159" s="9" t="s">
         <v>423</v>
       </c>
@@ -9126,7 +9129,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A160" s="9" t="s">
         <v>424</v>
       </c>
@@ -9197,7 +9200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A161" s="9" t="s">
         <v>425</v>
       </c>
@@ -9268,7 +9271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A164" s="9" t="s">
         <v>465</v>
       </c>
@@ -9276,7 +9279,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="165" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A165" s="9"/>
       <c r="B165" s="9" t="s">
         <v>479</v>
@@ -9340,7 +9343,7 @@
       <c r="AA165" s="9"/>
       <c r="AB165" s="9"/>
     </row>
-    <row r="166" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A166" s="9" t="s">
         <v>138</v>
       </c>
@@ -9416,7 +9419,7 @@
       </c>
       <c r="AB166" s="9"/>
     </row>
-    <row r="167" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A167" s="9" t="s">
         <v>127</v>
       </c>
@@ -9516,7 +9519,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="168" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A168" s="9" t="s">
         <v>128</v>
       </c>
@@ -9616,7 +9619,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="169" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A169" s="9" t="s">
         <v>129</v>
       </c>
@@ -9716,7 +9719,7 @@
       </c>
       <c r="AB169" s="66"/>
     </row>
-    <row r="170" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A170" s="9" t="s">
         <v>176</v>
       </c>
@@ -9816,7 +9819,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="171" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A171" s="9" t="s">
         <v>182</v>
       </c>
@@ -9916,7 +9919,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="172" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A172" s="9" t="s">
         <v>187</v>
       </c>
@@ -10016,7 +10019,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="173" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A173" s="9" t="s">
         <v>285</v>
       </c>
@@ -10116,7 +10119,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="174" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A174" s="9" t="s">
         <v>288</v>
       </c>
@@ -10216,7 +10219,7 @@
       </c>
       <c r="AB174" s="63"/>
     </row>
-    <row r="175" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A175" s="9" t="s">
         <v>290</v>
       </c>
@@ -10316,7 +10319,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="176" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A176" s="9" t="s">
         <v>291</v>
       </c>
@@ -10416,7 +10419,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="177" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A177" s="9" t="s">
         <v>420</v>
       </c>
@@ -10516,7 +10519,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="178" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A178" s="9" t="s">
         <v>421</v>
       </c>
@@ -10616,7 +10619,7 @@
       </c>
       <c r="AB178" s="63"/>
     </row>
-    <row r="179" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A179" s="9" t="s">
         <v>422</v>
       </c>
@@ -10716,7 +10719,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="180" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A180" s="9" t="s">
         <v>423</v>
       </c>
@@ -10816,7 +10819,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="181" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A181" s="9" t="s">
         <v>424</v>
       </c>
@@ -10916,7 +10919,7 @@
       </c>
       <c r="AB181" s="66"/>
     </row>
-    <row r="182" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A182" s="9" t="s">
         <v>425</v>
       </c>
@@ -11016,7 +11019,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="185" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:28" x14ac:dyDescent="0.35">
       <c r="P185" t="s">
         <v>288</v>
       </c>
@@ -11061,7 +11064,7 @@
         <v>0.71753333333333336</v>
       </c>
     </row>
-    <row r="187" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:28" x14ac:dyDescent="0.35">
       <c r="P187" t="s">
         <v>476</v>
       </c>
@@ -11106,7 +11109,7 @@
         <v>0.76733333333333331</v>
       </c>
     </row>
-    <row r="189" spans="1:28" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:28" x14ac:dyDescent="0.35">
       <c r="P189" t="s">
         <v>477</v>
       </c>
@@ -11170,26 +11173,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{871AEF4C-9567-4F69-A103-F367FD8FD456}">
   <dimension ref="A1:AD189"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.77734375" customWidth="1"/>
-    <col min="3" max="4" width="10.21875" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
+    <col min="1" max="1" width="19.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" customWidth="1"/>
+    <col min="3" max="4" width="10.1796875" customWidth="1"/>
+    <col min="5" max="5" width="20.453125" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.44140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
-    <col min="9" max="9" width="11.109375" customWidth="1"/>
-    <col min="10" max="11" width="14.44140625" customWidth="1"/>
-    <col min="12" max="13" width="15.77734375" customWidth="1"/>
+    <col min="7" max="7" width="27.453125" customWidth="1"/>
+    <col min="8" max="8" width="10.54296875" customWidth="1"/>
+    <col min="9" max="9" width="11.08984375" customWidth="1"/>
+    <col min="10" max="11" width="14.453125" customWidth="1"/>
+    <col min="12" max="13" width="15.81640625" customWidth="1"/>
     <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="11.44140625" customWidth="1"/>
-    <col min="17" max="17" width="20.21875" customWidth="1"/>
-    <col min="20" max="20" width="19.44140625" customWidth="1"/>
-    <col min="21" max="21" width="20.33203125" customWidth="1"/>
+    <col min="15" max="15" width="11.453125" customWidth="1"/>
+    <col min="17" max="17" width="20.1796875" customWidth="1"/>
+    <col min="20" max="20" width="19.453125" customWidth="1"/>
+    <col min="21" max="21" width="20.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>111</v>
       </c>
@@ -11197,7 +11200,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="9" t="s">
         <v>112</v>
       </c>
@@ -11205,7 +11208,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="3" spans="1:21" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:21" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="9" t="s">
         <v>17</v>
       </c>
@@ -11231,7 +11234,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:21" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="9" t="s">
         <v>18</v>
       </c>
@@ -11257,7 +11260,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:21" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
         <v>19</v>
       </c>
@@ -11283,7 +11286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:21" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:21" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
         <v>20</v>
       </c>
@@ -11309,7 +11312,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:21" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="9" t="s">
         <v>21</v>
       </c>
@@ -11329,7 +11332,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:21" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="9" t="s">
         <v>22</v>
       </c>
@@ -11349,7 +11352,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:21" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="9" t="s">
         <v>23</v>
       </c>
@@ -11369,7 +11372,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:21" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="9" t="s">
         <v>24</v>
       </c>
@@ -11377,7 +11380,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="31.8" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" ht="31.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A11" s="9" t="s">
         <v>25</v>
       </c>
@@ -11403,7 +11406,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A12" s="9"/>
       <c r="B12" s="17"/>
       <c r="G12" t="s">
@@ -11425,7 +11428,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B13" s="15"/>
       <c r="G13" t="s">
         <v>105</v>
@@ -11452,7 +11455,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:21" ht="29.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="B14" s="15"/>
       <c r="G14" t="s">
         <v>372</v>
@@ -11480,7 +11483,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" s="18" t="s">
         <v>110</v>
       </c>
@@ -11504,7 +11507,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" s="9"/>
       <c r="B16" s="15"/>
       <c r="G16" t="s">
@@ -11514,7 +11517,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A17" s="15" t="s">
         <v>112</v>
       </c>
@@ -11534,7 +11537,7 @@
       <c r="L17" s="3"/>
       <c r="M17" s="3"/>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>17</v>
       </c>
@@ -11557,7 +11560,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>18</v>
       </c>
@@ -11580,7 +11583,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>19</v>
       </c>
@@ -11609,7 +11612,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>20</v>
       </c>
@@ -11644,7 +11647,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
         <v>21</v>
       </c>
@@ -11673,7 +11676,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
         <v>22</v>
       </c>
@@ -11703,7 +11706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
         <v>23</v>
       </c>
@@ -11733,7 +11736,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
         <v>24</v>
       </c>
@@ -11763,7 +11766,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
         <v>25</v>
       </c>
@@ -11793,7 +11796,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A27" s="9"/>
       <c r="B27" s="15"/>
       <c r="C27" s="15">
@@ -11821,7 +11824,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:21" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="42" t="s">
@@ -11834,12 +11837,12 @@
         <v>478</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A30" s="18" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A32" s="15" t="s">
         <v>112</v>
       </c>
@@ -11847,7 +11850,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="33" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A33" s="9" t="s">
         <v>17</v>
       </c>
@@ -11855,7 +11858,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A34" s="9" t="s">
         <v>18</v>
       </c>
@@ -11866,7 +11869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A35" s="9" t="s">
         <v>19</v>
       </c>
@@ -11877,7 +11880,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A36" s="9" t="s">
         <v>20</v>
       </c>
@@ -11888,7 +11891,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A37" s="9" t="s">
         <v>21</v>
       </c>
@@ -11899,7 +11902,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A38" s="9" t="s">
         <v>22</v>
       </c>
@@ -11910,7 +11913,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="9" t="s">
         <v>23</v>
       </c>
@@ -11921,7 +11924,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A40" s="9" t="s">
         <v>24</v>
       </c>
@@ -11932,7 +11935,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:15" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A41" s="9" t="s">
         <v>25</v>
       </c>
@@ -11943,29 +11946,29 @@
         <v>151</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="E42" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="E43" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="E44" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A47" s="18"/>
       <c r="L47" t="s">
         <v>496</v>
@@ -11974,7 +11977,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A48" s="33" t="s">
         <v>109</v>
       </c>
@@ -12015,7 +12018,7 @@
       </c>
       <c r="O48" s="16"/>
     </row>
-    <row r="49" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A49" s="35" t="s">
         <v>127</v>
       </c>
@@ -12056,7 +12059,7 @@
       </c>
       <c r="O49" s="12"/>
     </row>
-    <row r="50" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A50" s="35" t="s">
         <v>128</v>
       </c>
@@ -12097,7 +12100,7 @@
       </c>
       <c r="O50" s="12"/>
     </row>
-    <row r="51" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A51" s="35" t="s">
         <v>129</v>
       </c>
@@ -12138,7 +12141,7 @@
       </c>
       <c r="O51" s="12"/>
     </row>
-    <row r="52" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A52" s="35" t="s">
         <v>176</v>
       </c>
@@ -12148,7 +12151,7 @@
       <c r="C52" s="36">
         <v>667.66700000000003</v>
       </c>
-      <c r="D52" s="36">
+      <c r="D52" s="104">
         <v>3</v>
       </c>
       <c r="E52" s="36" t="s">
@@ -12178,7 +12181,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A53" s="35" t="s">
         <v>182</v>
       </c>
@@ -12218,7 +12221,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="54" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A54" s="35" t="s">
         <v>187</v>
       </c>
@@ -12258,7 +12261,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A55" s="35" t="s">
         <v>285</v>
       </c>
@@ -12298,7 +12301,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="56" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A56" s="35" t="s">
         <v>288</v>
       </c>
@@ -12339,7 +12342,7 @@
       </c>
       <c r="O56" s="9"/>
     </row>
-    <row r="57" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="35" t="s">
         <v>290</v>
       </c>
@@ -12380,7 +12383,7 @@
       </c>
       <c r="O57" s="12"/>
     </row>
-    <row r="58" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A58" s="35" t="s">
         <v>291</v>
       </c>
@@ -12421,7 +12424,7 @@
       </c>
       <c r="O58" s="12"/>
     </row>
-    <row r="59" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A59" s="35" t="s">
         <v>420</v>
       </c>
@@ -12462,7 +12465,7 @@
       </c>
       <c r="O59" s="12"/>
     </row>
-    <row r="60" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A60" s="35" t="s">
         <v>421</v>
       </c>
@@ -12503,7 +12506,7 @@
       </c>
       <c r="O60" s="12"/>
     </row>
-    <row r="61" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A61" s="35" t="s">
         <v>422</v>
       </c>
@@ -12544,7 +12547,7 @@
       </c>
       <c r="O61" s="12"/>
     </row>
-    <row r="62" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A62" s="35" t="s">
         <v>423</v>
       </c>
@@ -12585,7 +12588,7 @@
       </c>
       <c r="O62" s="12"/>
     </row>
-    <row r="63" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A63" s="35" t="s">
         <v>424</v>
       </c>
@@ -12626,7 +12629,7 @@
       </c>
       <c r="O63" s="12"/>
     </row>
-    <row r="64" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A64" s="35" t="s">
         <v>425</v>
       </c>
@@ -12667,18 +12670,18 @@
       </c>
       <c r="O64" s="12"/>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A66" s="37" t="s">
         <v>309</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:14" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="J67" s="37" t="s">
         <v>494</v>
       </c>
       <c r="K67" s="37"/>
     </row>
-    <row r="68" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:14" ht="15.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A68" s="38" t="s">
         <v>138</v>
       </c>
@@ -12711,7 +12714,7 @@
       </c>
       <c r="K68" s="90"/>
     </row>
-    <row r="69" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A69" s="40" t="s">
         <v>127</v>
       </c>
@@ -12744,7 +12747,7 @@
       </c>
       <c r="K69" s="73"/>
     </row>
-    <row r="70" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A70" s="40" t="s">
         <v>128</v>
       </c>
@@ -12778,7 +12781,7 @@
       <c r="K70" s="73"/>
       <c r="N70" s="9"/>
     </row>
-    <row r="71" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A71" s="40" t="s">
         <v>129</v>
       </c>
@@ -12812,7 +12815,7 @@
       <c r="K71" s="73"/>
       <c r="N71" s="9"/>
     </row>
-    <row r="72" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A72" s="40" t="s">
         <v>176</v>
       </c>
@@ -12848,7 +12851,7 @@
       <c r="M72" s="9"/>
       <c r="N72" s="9"/>
     </row>
-    <row r="73" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A73" s="40" t="s">
         <v>182</v>
       </c>
@@ -12884,7 +12887,7 @@
       <c r="M73" s="9"/>
       <c r="N73" s="9"/>
     </row>
-    <row r="74" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A74" s="40" t="s">
         <v>187</v>
       </c>
@@ -12920,7 +12923,7 @@
       <c r="M74" s="9"/>
       <c r="N74" s="9"/>
     </row>
-    <row r="75" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A75" s="40" t="s">
         <v>285</v>
       </c>
@@ -12956,7 +12959,7 @@
       <c r="M75" s="9"/>
       <c r="N75" s="9"/>
     </row>
-    <row r="76" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A76" s="40" t="s">
         <v>288</v>
       </c>
@@ -12992,7 +12995,7 @@
       <c r="M76" s="9"/>
       <c r="N76" s="9"/>
     </row>
-    <row r="77" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A77" s="40" t="s">
         <v>290</v>
       </c>
@@ -13028,7 +13031,7 @@
       <c r="M77" s="9"/>
       <c r="N77" s="9"/>
     </row>
-    <row r="78" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="40" t="s">
         <v>291</v>
       </c>
@@ -13064,7 +13067,7 @@
       <c r="M78" s="9"/>
       <c r="N78" s="9"/>
     </row>
-    <row r="79" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="40" t="s">
         <v>420</v>
       </c>
@@ -13100,7 +13103,7 @@
       <c r="M79" s="9"/>
       <c r="N79" s="9"/>
     </row>
-    <row r="80" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A80" s="40" t="s">
         <v>421</v>
       </c>
@@ -13136,7 +13139,7 @@
       <c r="M80" s="9"/>
       <c r="N80" s="9"/>
     </row>
-    <row r="81" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A81" s="40" t="s">
         <v>422</v>
       </c>
@@ -13172,7 +13175,7 @@
       <c r="M81" s="9"/>
       <c r="N81" s="9"/>
     </row>
-    <row r="82" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A82" s="40" t="s">
         <v>423</v>
       </c>
@@ -13208,7 +13211,7 @@
       <c r="M82" s="9"/>
       <c r="N82" s="9"/>
     </row>
-    <row r="83" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A83" s="40" t="s">
         <v>424</v>
       </c>
@@ -13244,7 +13247,7 @@
       <c r="M83" s="9"/>
       <c r="N83" s="9"/>
     </row>
-    <row r="84" spans="1:14" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A84" s="40" t="s">
         <v>425</v>
       </c>
@@ -13280,12 +13283,12 @@
       <c r="M84" s="9"/>
       <c r="N84" s="9"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A86" s="18" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>140</v>
       </c>
@@ -13296,7 +13299,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>127</v>
       </c>
@@ -13319,7 +13322,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>128</v>
       </c>
@@ -13342,7 +13345,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>129</v>
       </c>
@@ -13365,7 +13368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>176</v>
       </c>
@@ -13388,7 +13391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>182</v>
       </c>
@@ -13411,7 +13414,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>187</v>
       </c>
@@ -13434,7 +13437,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>285</v>
       </c>
@@ -13457,7 +13460,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>288</v>
       </c>
@@ -13480,7 +13483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>290</v>
       </c>
@@ -13503,7 +13506,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="99" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>291</v>
       </c>
@@ -13526,7 +13529,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="100" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>420</v>
       </c>
@@ -13549,7 +13552,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="101" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>421</v>
       </c>
@@ -13572,7 +13575,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="102" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>422</v>
       </c>
@@ -13596,7 +13599,7 @@
       </c>
       <c r="M102" s="81"/>
     </row>
-    <row r="103" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>423</v>
       </c>
@@ -13619,7 +13622,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="104" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>424</v>
       </c>
@@ -13642,7 +13645,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="105" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>425</v>
       </c>
@@ -13665,7 +13668,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>223</v>
       </c>
@@ -13676,7 +13679,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>127</v>
       </c>
@@ -13699,7 +13702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>128</v>
       </c>
@@ -13722,7 +13725,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="110" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>129</v>
       </c>
@@ -13745,7 +13748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>176</v>
       </c>
@@ -13768,7 +13771,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="112" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>182</v>
       </c>
@@ -13791,7 +13794,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="113" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>187</v>
       </c>
@@ -13814,7 +13817,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="114" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>285</v>
       </c>
@@ -13837,7 +13840,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="115" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>288</v>
       </c>
@@ -13860,7 +13863,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="116" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>290</v>
       </c>
@@ -13883,7 +13886,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="117" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>291</v>
       </c>
@@ -13906,7 +13909,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="118" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>420</v>
       </c>
@@ -13929,7 +13932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>421</v>
       </c>
@@ -13952,7 +13955,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="120" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>422</v>
       </c>
@@ -13975,7 +13978,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="121" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>423</v>
       </c>
@@ -13998,7 +14001,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="122" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>424</v>
       </c>
@@ -14021,7 +14024,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="123" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>425</v>
       </c>
@@ -14044,7 +14047,7 @@
         <v>0.4</v>
       </c>
     </row>
-    <row r="125" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>145</v>
       </c>
@@ -14065,7 +14068,7 @@
       <c r="R125" s="85"/>
       <c r="S125" s="85"/>
     </row>
-    <row r="126" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>127</v>
       </c>
@@ -14100,7 +14103,7 @@
       <c r="R126" s="85"/>
       <c r="S126" s="85"/>
     </row>
-    <row r="127" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>128</v>
       </c>
@@ -14135,7 +14138,7 @@
       <c r="R127" s="85"/>
       <c r="S127" s="85"/>
     </row>
-    <row r="128" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>129</v>
       </c>
@@ -14170,7 +14173,7 @@
       <c r="R128" s="85"/>
       <c r="S128" s="85"/>
     </row>
-    <row r="129" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>176</v>
       </c>
@@ -14205,7 +14208,7 @@
       <c r="R129" s="85"/>
       <c r="S129" s="85"/>
     </row>
-    <row r="130" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>182</v>
       </c>
@@ -14240,7 +14243,7 @@
       <c r="R130" s="85"/>
       <c r="S130" s="85"/>
     </row>
-    <row r="131" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>187</v>
       </c>
@@ -14275,7 +14278,7 @@
       <c r="R131" s="85"/>
       <c r="S131" s="85"/>
     </row>
-    <row r="132" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>285</v>
       </c>
@@ -14310,7 +14313,7 @@
       <c r="R132" s="85"/>
       <c r="S132" s="85"/>
     </row>
-    <row r="133" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>288</v>
       </c>
@@ -14345,7 +14348,7 @@
       <c r="R133" s="85"/>
       <c r="S133" s="85"/>
     </row>
-    <row r="134" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>290</v>
       </c>
@@ -14380,7 +14383,7 @@
       <c r="R134" s="85"/>
       <c r="S134" s="85"/>
     </row>
-    <row r="135" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>291</v>
       </c>
@@ -14415,7 +14418,7 @@
       <c r="R135" s="85"/>
       <c r="S135" s="85"/>
     </row>
-    <row r="136" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>420</v>
       </c>
@@ -14450,7 +14453,7 @@
       <c r="R136" s="85"/>
       <c r="S136" s="85"/>
     </row>
-    <row r="137" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>421</v>
       </c>
@@ -14485,7 +14488,7 @@
       <c r="R137" s="85"/>
       <c r="S137" s="85"/>
     </row>
-    <row r="138" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>422</v>
       </c>
@@ -14520,7 +14523,7 @@
       <c r="R138" s="85"/>
       <c r="S138" s="85"/>
     </row>
-    <row r="139" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>423</v>
       </c>
@@ -14555,7 +14558,7 @@
       <c r="R139" s="85"/>
       <c r="S139" s="85"/>
     </row>
-    <row r="140" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>424</v>
       </c>
@@ -14590,7 +14593,7 @@
       <c r="R140" s="85"/>
       <c r="S140" s="85"/>
     </row>
-    <row r="141" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>425</v>
       </c>
@@ -14625,7 +14628,7 @@
       <c r="R141" s="85"/>
       <c r="S141" s="85"/>
     </row>
-    <row r="142" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:19" x14ac:dyDescent="0.35">
       <c r="L142" t="s">
         <v>495</v>
       </c>
@@ -14633,12 +14636,12 @@
         <v>498</v>
       </c>
     </row>
-    <row r="143" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="144" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:19" x14ac:dyDescent="0.35">
       <c r="J144" t="s">
         <v>495</v>
       </c>
@@ -14646,7 +14649,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="145" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A145" s="9" t="s">
         <v>138</v>
       </c>
@@ -14714,7 +14717,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="146" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A146" s="9" t="s">
         <v>127</v>
       </c>
@@ -14792,7 +14795,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A147" s="9" t="s">
         <v>128</v>
       </c>
@@ -14870,7 +14873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A148" s="9" t="s">
         <v>129</v>
       </c>
@@ -14948,7 +14951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A149" s="9" t="s">
         <v>176</v>
       </c>
@@ -15026,7 +15029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A150" s="9" t="s">
         <v>182</v>
       </c>
@@ -15104,7 +15107,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A151" s="9" t="s">
         <v>187</v>
       </c>
@@ -15182,7 +15185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A152" s="9" t="s">
         <v>285</v>
       </c>
@@ -15260,7 +15263,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="153" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A153" s="9" t="s">
         <v>288</v>
       </c>
@@ -15338,7 +15341,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="154" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A154" s="9" t="s">
         <v>290</v>
       </c>
@@ -15416,7 +15419,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="155" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A155" s="9" t="s">
         <v>291</v>
       </c>
@@ -15493,7 +15496,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="156" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A156" s="9" t="s">
         <v>420</v>
       </c>
@@ -15570,7 +15573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A157" s="9" t="s">
         <v>421</v>
       </c>
@@ -15647,7 +15650,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="158" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A158" s="9" t="s">
         <v>422</v>
       </c>
@@ -15724,7 +15727,7 @@
         <v>0.33333333333333331</v>
       </c>
     </row>
-    <row r="159" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A159" s="9" t="s">
         <v>423</v>
       </c>
@@ -15801,7 +15804,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="160" spans="1:27" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A160" s="9" t="s">
         <v>424</v>
       </c>
@@ -15878,7 +15881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A161" s="9" t="s">
         <v>425</v>
       </c>
@@ -15955,7 +15958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A164" s="9" t="s">
         <v>465</v>
       </c>
@@ -15969,7 +15972,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="165" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A165" s="9"/>
       <c r="B165" s="9" t="s">
         <v>479</v>
@@ -16038,7 +16041,7 @@
       <c r="AC165" s="9"/>
       <c r="AD165" s="9"/>
     </row>
-    <row r="166" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A166" s="9" t="s">
         <v>138</v>
       </c>
@@ -16117,7 +16120,7 @@
       </c>
       <c r="AD166" s="9"/>
     </row>
-    <row r="167" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A167" s="9" t="s">
         <v>127</v>
       </c>
@@ -16221,7 +16224,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="168" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A168" s="9" t="s">
         <v>128</v>
       </c>
@@ -16325,7 +16328,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="169" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A169" s="9" t="s">
         <v>129</v>
       </c>
@@ -16427,7 +16430,7 @@
       </c>
       <c r="AD169" s="66"/>
     </row>
-    <row r="170" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A170" s="9" t="s">
         <v>176</v>
       </c>
@@ -16531,7 +16534,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="171" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A171" s="9" t="s">
         <v>182</v>
       </c>
@@ -16635,7 +16638,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="172" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A172" s="9" t="s">
         <v>187</v>
       </c>
@@ -16739,7 +16742,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="173" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A173" s="9" t="s">
         <v>285</v>
       </c>
@@ -16843,7 +16846,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="174" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A174" s="9" t="s">
         <v>288</v>
       </c>
@@ -16945,7 +16948,7 @@
       </c>
       <c r="AD174" s="63"/>
     </row>
-    <row r="175" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A175" s="9" t="s">
         <v>290</v>
       </c>
@@ -17049,7 +17052,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="176" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A176" s="9" t="s">
         <v>291</v>
       </c>
@@ -17153,7 +17156,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="177" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A177" s="9" t="s">
         <v>420</v>
       </c>
@@ -17257,7 +17260,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="178" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A178" s="9" t="s">
         <v>421</v>
       </c>
@@ -17359,7 +17362,7 @@
       </c>
       <c r="AD178" s="63"/>
     </row>
-    <row r="179" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A179" s="9" t="s">
         <v>422</v>
       </c>
@@ -17463,7 +17466,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="180" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A180" s="9" t="s">
         <v>423</v>
       </c>
@@ -17567,7 +17570,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="181" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A181" s="9" t="s">
         <v>424</v>
       </c>
@@ -17669,7 +17672,7 @@
       </c>
       <c r="AD181" s="66"/>
     </row>
-    <row r="182" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A182" s="9" t="s">
         <v>425</v>
       </c>
@@ -17773,7 +17776,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="185" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:30" x14ac:dyDescent="0.35">
       <c r="R185" t="s">
         <v>288</v>
       </c>
@@ -17818,7 +17821,7 @@
         <v>0.71353333333333335</v>
       </c>
     </row>
-    <row r="187" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:30" x14ac:dyDescent="0.35">
       <c r="R187" t="s">
         <v>476</v>
       </c>
@@ -17863,7 +17866,7 @@
         <v>0.76333333333333331</v>
       </c>
     </row>
-    <row r="189" spans="1:30" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:30" x14ac:dyDescent="0.35">
       <c r="R189" t="s">
         <v>477</v>
       </c>
@@ -17917,15 +17920,15 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A2CA57A-A845-4DC7-9421-80539E659A63}">
   <dimension ref="A1:D10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.33203125" customWidth="1"/>
-    <col min="2" max="2" width="24.109375" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="33.109375" customWidth="1"/>
+    <col min="1" max="1" width="12.36328125" customWidth="1"/>
+    <col min="2" max="2" width="24.08984375" customWidth="1"/>
+    <col min="3" max="3" width="16.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="9" t="s">
         <v>112</v>
       </c>
@@ -17936,7 +17939,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="9" t="s">
         <v>17</v>
       </c>
@@ -17952,7 +17955,7 @@
         <v>0.31432980599647264</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A3" s="9" t="s">
         <v>18</v>
       </c>
@@ -17964,7 +17967,7 @@
         <v>0.27420634920634918</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A4" s="9" t="s">
         <v>19</v>
       </c>
@@ -17976,7 +17979,7 @@
         <v>0.28809523809523802</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="9" t="s">
         <v>20</v>
       </c>
@@ -17984,7 +17987,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="9" t="s">
         <v>21</v>
       </c>
@@ -17992,7 +17995,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="9" t="s">
         <v>22</v>
       </c>
@@ -18000,7 +18003,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="9" t="s">
         <v>23</v>
       </c>
@@ -18008,7 +18011,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A9" s="9" t="s">
         <v>24</v>
       </c>
@@ -18016,7 +18019,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" ht="16" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="9" t="s">
         <v>25</v>
       </c>
@@ -18032,28 +18035,28 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B6626FB-65A5-4DCB-9E1D-A2FA0EB2B8E1}">
   <dimension ref="A1:T119"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="19.6640625" customWidth="1"/>
-    <col min="2" max="2" width="18.77734375" customWidth="1"/>
-    <col min="3" max="5" width="13.21875" customWidth="1"/>
-    <col min="6" max="8" width="20.44140625" customWidth="1"/>
-    <col min="9" max="9" width="18.44140625" customWidth="1"/>
-    <col min="10" max="10" width="17.6640625" customWidth="1"/>
+    <col min="1" max="1" width="19.6328125" customWidth="1"/>
+    <col min="2" max="2" width="18.81640625" customWidth="1"/>
+    <col min="3" max="5" width="13.1796875" customWidth="1"/>
+    <col min="6" max="8" width="20.453125" customWidth="1"/>
+    <col min="9" max="9" width="18.453125" customWidth="1"/>
+    <col min="10" max="10" width="17.6328125" customWidth="1"/>
     <col min="11" max="11" width="17" customWidth="1"/>
-    <col min="12" max="12" width="10.5546875" customWidth="1"/>
-    <col min="13" max="13" width="11.109375" customWidth="1"/>
-    <col min="14" max="14" width="14.44140625" customWidth="1"/>
-    <col min="15" max="15" width="15.77734375" customWidth="1"/>
+    <col min="12" max="12" width="10.54296875" customWidth="1"/>
+    <col min="13" max="13" width="11.08984375" customWidth="1"/>
+    <col min="14" max="14" width="14.453125" customWidth="1"/>
+    <col min="15" max="15" width="15.81640625" customWidth="1"/>
     <col min="16" max="16" width="13" customWidth="1"/>
-    <col min="17" max="17" width="11.44140625" customWidth="1"/>
-    <col min="18" max="18" width="18.44140625" customWidth="1"/>
-    <col min="19" max="19" width="22.21875" customWidth="1"/>
-    <col min="20" max="20" width="33.109375" customWidth="1"/>
-    <col min="24" max="24" width="17.44140625" customWidth="1"/>
+    <col min="17" max="17" width="11.453125" customWidth="1"/>
+    <col min="18" max="18" width="18.453125" customWidth="1"/>
+    <col min="19" max="19" width="22.1796875" customWidth="1"/>
+    <col min="20" max="20" width="33.08984375" customWidth="1"/>
+    <col min="24" max="24" width="17.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>111</v>
       </c>
@@ -18061,7 +18064,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" s="9" t="s">
         <v>112</v>
       </c>
@@ -18069,7 +18072,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" s="9" t="s">
         <v>17</v>
       </c>
@@ -18095,7 +18098,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="9" t="s">
         <v>18</v>
       </c>
@@ -18124,7 +18127,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="9" t="s">
         <v>19</v>
       </c>
@@ -18153,7 +18156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:20" ht="58" x14ac:dyDescent="0.35">
       <c r="A6" s="9" t="s">
         <v>20</v>
       </c>
@@ -18182,7 +18185,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:20" ht="58" x14ac:dyDescent="0.35">
       <c r="A7" s="9" t="s">
         <v>21</v>
       </c>
@@ -18211,7 +18214,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:20" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A8" s="9" t="s">
         <v>22</v>
       </c>
@@ -18240,7 +18243,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" s="9" t="s">
         <v>23</v>
       </c>
@@ -18248,7 +18251,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10" s="9" t="s">
         <v>24</v>
       </c>
@@ -18256,7 +18259,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" s="9" t="s">
         <v>25</v>
       </c>
@@ -18282,7 +18285,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" s="9"/>
       <c r="B12" s="17"/>
       <c r="J12" t="s">
@@ -18304,7 +18307,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="B13" s="15"/>
       <c r="J13" t="s">
         <v>194</v>
@@ -18325,7 +18328,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="B14" s="15"/>
       <c r="J14" t="s">
         <v>195</v>
@@ -18346,7 +18349,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15" s="18" t="s">
         <v>110</v>
       </c>
@@ -18364,7 +18367,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" s="9"/>
       <c r="B16" s="15"/>
       <c r="J16" t="s">
@@ -18380,7 +18383,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A17" s="17" t="s">
         <v>112</v>
       </c>
@@ -18402,7 +18405,7 @@
       <c r="G17" s="9"/>
       <c r="O17" s="3"/>
     </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A18" s="9" t="s">
         <v>17</v>
       </c>
@@ -18434,7 +18437,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19" s="9" t="s">
         <v>18</v>
       </c>
@@ -18466,7 +18469,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20" s="9" t="s">
         <v>19</v>
       </c>
@@ -18498,7 +18501,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21" s="9" t="s">
         <v>20</v>
       </c>
@@ -18542,7 +18545,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22" s="9" t="s">
         <v>21</v>
       </c>
@@ -18589,7 +18592,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23" s="9" t="s">
         <v>22</v>
       </c>
@@ -18630,7 +18633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A24" s="9" t="s">
         <v>23</v>
       </c>
@@ -18671,7 +18674,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:20" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:20" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A25" s="9" t="s">
         <v>24</v>
       </c>
@@ -18712,7 +18715,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:20" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:20" ht="58" x14ac:dyDescent="0.35">
       <c r="A26" s="9" t="s">
         <v>25</v>
       </c>
@@ -18753,7 +18756,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27" s="9"/>
       <c r="B27" s="17"/>
       <c r="C27" s="17">
@@ -18775,19 +18778,19 @@
       <c r="G27" s="9"/>
       <c r="H27" s="22"/>
     </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28" s="4"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
     </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A30" s="18" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="32" spans="1:20" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:20" ht="29" x14ac:dyDescent="0.35">
       <c r="A32" s="17" t="s">
         <v>112</v>
       </c>
@@ -18815,7 +18818,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33" s="9" t="s">
         <v>17</v>
       </c>
@@ -18845,7 +18848,7 @@
         <v>31.432980599647259</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34" s="9" t="s">
         <v>18</v>
       </c>
@@ -18875,7 +18878,7 @@
         <v>20.321869488536155</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35" s="9" t="s">
         <v>19</v>
       </c>
@@ -18905,7 +18908,7 @@
         <v>14.766313932980598</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36" s="9" t="s">
         <v>20</v>
       </c>
@@ -18935,7 +18938,7 @@
         <v>11.062610229276896</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" s="9" t="s">
         <v>21</v>
       </c>
@@ -18965,7 +18968,7 @@
         <v>8.284832451499117</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38" s="9" t="s">
         <v>22</v>
       </c>
@@ -18997,7 +19000,7 @@
       <c r="R38" s="3"/>
       <c r="S38" s="3"/>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39" s="9" t="s">
         <v>23</v>
       </c>
@@ -19029,7 +19032,7 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40" s="9" t="s">
         <v>24</v>
       </c>
@@ -19061,7 +19064,7 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41" s="9" t="s">
         <v>25</v>
       </c>
@@ -19091,7 +19094,7 @@
         <v>1.2345679012345678</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -19112,15 +19115,15 @@
         <v>99.999999999999986</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46" s="9" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A47" s="18"/>
     </row>
-    <row r="48" spans="1:19" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:19" ht="29" x14ac:dyDescent="0.35">
       <c r="A48" s="16" t="s">
         <v>44</v>
       </c>
@@ -19161,7 +19164,7 @@
       <c r="P48" s="16"/>
       <c r="Q48" s="16"/>
     </row>
-    <row r="49" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A49" s="16" t="s">
         <v>127</v>
       </c>
@@ -19202,7 +19205,7 @@
       <c r="P49" s="12"/>
       <c r="Q49" s="12"/>
     </row>
-    <row r="50" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A50" s="16" t="s">
         <v>128</v>
       </c>
@@ -19243,7 +19246,7 @@
       <c r="P50" s="12"/>
       <c r="Q50" s="12"/>
     </row>
-    <row r="51" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A51" s="16" t="s">
         <v>129</v>
       </c>
@@ -19284,7 +19287,7 @@
       <c r="P51" s="12"/>
       <c r="Q51" s="12"/>
     </row>
-    <row r="52" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A52" s="16" t="s">
         <v>176</v>
       </c>
@@ -19323,7 +19326,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A53" s="16" t="s">
         <v>182</v>
       </c>
@@ -19362,7 +19365,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A54" s="16" t="s">
         <v>187</v>
       </c>
@@ -19401,7 +19404,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A56" s="9" t="s">
         <v>109</v>
       </c>
@@ -19442,7 +19445,7 @@
       <c r="Q56" s="9"/>
       <c r="R56" s="9"/>
     </row>
-    <row r="57" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A57" s="9" t="s">
         <v>127</v>
       </c>
@@ -19483,7 +19486,7 @@
       <c r="Q57" s="9"/>
       <c r="R57" s="17"/>
     </row>
-    <row r="58" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A58" s="9" t="s">
         <v>128</v>
       </c>
@@ -19524,7 +19527,7 @@
       <c r="Q58" s="9"/>
       <c r="R58" s="17"/>
     </row>
-    <row r="59" spans="1:18" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="A59" s="9" t="s">
         <v>129</v>
       </c>
@@ -19565,7 +19568,7 @@
       <c r="Q59" s="9"/>
       <c r="R59" s="17"/>
     </row>
-    <row r="60" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A60" s="9" t="s">
         <v>176</v>
       </c>
@@ -19606,7 +19609,7 @@
       <c r="Q60" s="9"/>
       <c r="R60" s="17"/>
     </row>
-    <row r="61" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A61" s="9" t="s">
         <v>182</v>
       </c>
@@ -19647,7 +19650,7 @@
       <c r="Q61" s="9"/>
       <c r="R61" s="17"/>
     </row>
-    <row r="62" spans="1:18" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A62" s="9" t="s">
         <v>187</v>
       </c>
@@ -19688,22 +19691,22 @@
       <c r="Q62" s="9"/>
       <c r="R62" s="17"/>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.35">
       <c r="Q63" s="9"/>
       <c r="R63" s="17"/>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>137</v>
       </c>
       <c r="Q64" s="9"/>
       <c r="R64" s="17"/>
     </row>
-    <row r="65" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:18" x14ac:dyDescent="0.35">
       <c r="Q65" s="9"/>
       <c r="R65" s="17"/>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A66" s="9" t="s">
         <v>138</v>
       </c>
@@ -19740,7 +19743,7 @@
       </c>
       <c r="O66" s="9"/>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A67" s="9" t="s">
         <v>127</v>
       </c>
@@ -19777,7 +19780,7 @@
       </c>
       <c r="O67" s="9"/>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A68" s="9" t="s">
         <v>128</v>
       </c>
@@ -19814,7 +19817,7 @@
       </c>
       <c r="O68" s="9"/>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A69" s="9" t="s">
         <v>129</v>
       </c>
@@ -19851,7 +19854,7 @@
       </c>
       <c r="O69" s="9"/>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A70" s="9" t="s">
         <v>176</v>
       </c>
@@ -19888,7 +19891,7 @@
       </c>
       <c r="O70" s="9"/>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A71" s="9" t="s">
         <v>182</v>
       </c>
@@ -19925,7 +19928,7 @@
       </c>
       <c r="O71" s="9"/>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A72" s="9" t="s">
         <v>187</v>
       </c>
@@ -19962,15 +19965,15 @@
       </c>
       <c r="O72" s="9"/>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.35">
       <c r="N73" s="9"/>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A74" s="18" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>140</v>
       </c>
@@ -19981,7 +19984,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>127</v>
       </c>
@@ -20004,7 +20007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>128</v>
       </c>
@@ -20027,7 +20030,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>129</v>
       </c>
@@ -20050,7 +20053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>176</v>
       </c>
@@ -20073,7 +20076,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="82" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>182</v>
       </c>
@@ -20096,7 +20099,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="83" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>187</v>
       </c>
@@ -20119,7 +20122,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="85" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>223</v>
       </c>
@@ -20130,7 +20133,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="86" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>127</v>
       </c>
@@ -20153,7 +20156,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="87" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>128</v>
       </c>
@@ -20176,7 +20179,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="88" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>129</v>
       </c>
@@ -20199,7 +20202,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="89" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>176</v>
       </c>
@@ -20222,7 +20225,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>182</v>
       </c>
@@ -20245,7 +20248,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>187</v>
       </c>
@@ -20268,7 +20271,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>220</v>
       </c>
@@ -20279,7 +20282,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>127</v>
       </c>
@@ -20303,7 +20306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>128</v>
       </c>
@@ -20327,7 +20330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>129</v>
       </c>
@@ -20350,7 +20353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>176</v>
       </c>
@@ -20373,7 +20376,7 @@
         <v>0.66666666666666663</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>182</v>
       </c>
@@ -20396,7 +20399,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>187</v>
       </c>
@@ -20419,16 +20422,16 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
       <c r="J100" s="19"/>
       <c r="O100" s="19"/>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A103" s="9" t="s">
         <v>138</v>
       </c>
@@ -20465,7 +20468,7 @@
       </c>
       <c r="P103" s="9"/>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A104" s="9" t="s">
         <v>127</v>
       </c>
@@ -20511,7 +20514,7 @@
       </c>
       <c r="P104" s="20"/>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A105" s="9" t="s">
         <v>128</v>
       </c>
@@ -20557,7 +20560,7 @@
       </c>
       <c r="P105" s="20"/>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A106" s="9" t="s">
         <v>129</v>
       </c>
@@ -20603,7 +20606,7 @@
       </c>
       <c r="P106" s="9"/>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A107" s="9" t="s">
         <v>176</v>
       </c>
@@ -20650,7 +20653,7 @@
       <c r="O107" s="9"/>
       <c r="P107" s="9"/>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A108" s="9" t="s">
         <v>182</v>
       </c>
@@ -20695,7 +20698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A109" s="9" t="s">
         <v>187</v>
       </c>
@@ -20740,12 +20743,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A113" s="9" t="s">
         <v>138</v>
       </c>
@@ -20787,7 +20790,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A114" s="9" t="s">
         <v>127</v>
       </c>
@@ -20840,7 +20843,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A115" s="9" t="s">
         <v>128</v>
       </c>
@@ -20893,7 +20896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A116" s="9" t="s">
         <v>129</v>
       </c>
@@ -20946,7 +20949,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A117" s="9" t="s">
         <v>176</v>
       </c>
@@ -21000,7 +21003,7 @@
       </c>
       <c r="R117" s="9"/>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A118" s="9" t="s">
         <v>182</v>
       </c>
@@ -21053,7 +21056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A119" s="9" t="s">
         <v>187</v>
       </c>
@@ -21122,15 +21125,15 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7917028-436B-4FE2-9CD4-951DC7160D43}">
   <dimension ref="A1:N25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.44140625" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" customWidth="1"/>
-    <col min="7" max="7" width="18.109375" customWidth="1"/>
-    <col min="10" max="10" width="18.5546875" customWidth="1"/>
+    <col min="1" max="1" width="20.453125" customWidth="1"/>
+    <col min="4" max="4" width="19.90625" customWidth="1"/>
+    <col min="7" max="7" width="18.08984375" customWidth="1"/>
+    <col min="10" max="10" width="18.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -21141,7 +21144,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -21153,7 +21156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -21165,7 +21168,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -21177,7 +21180,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -21189,7 +21192,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>4</v>
       </c>
@@ -21201,7 +21204,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -21213,7 +21216,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>6</v>
       </c>
@@ -21225,7 +21228,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -21237,7 +21240,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -21249,7 +21252,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -21261,13 +21264,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B12">
         <f>SUM(B2:B11)</f>
         <v>100</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -21281,7 +21284,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -21313,7 +21316,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -21345,7 +21348,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>1</v>
       </c>
@@ -21377,7 +21380,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>2</v>
       </c>
@@ -21409,7 +21412,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -21441,7 +21444,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>4</v>
       </c>
@@ -21473,7 +21476,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>5</v>
       </c>
@@ -21505,7 +21508,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>6</v>
       </c>
@@ -21537,7 +21540,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>7</v>
       </c>
@@ -21569,7 +21572,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>8</v>
       </c>
@@ -21601,7 +21604,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>9</v>
       </c>
@@ -21633,7 +21636,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="B25">
         <f>SUM(B15:B24)</f>
         <v>100</v>

--- a/Excel/STUDI KASUS.xlsx
+++ b/Excel/STUDI KASUS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KULIAH\SEMESTER 7\PROPOSAL SKRIPSI\skripsi\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50C85728-27EE-4038-B521-314B4788FF5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D4CF4A9-C805-4752-AA93-5C94D83DCA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="691" activeTab="3" xr2:uid="{901D0503-6946-40CA-8D36-37B156763246}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2357" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2356" uniqueCount="509">
   <si>
     <t xml:space="preserve">Biaya </t>
   </si>
@@ -1626,6 +1626,12 @@
   </si>
   <si>
     <t>Ac, spring bed, lemari, wc Dalam, wifi, tempat parkir, electric hoist</t>
+  </si>
+  <si>
+    <t>&lt;= 1km</t>
+  </si>
+  <si>
+    <t>&gt; 3km</t>
   </si>
 </sst>
 </file>
@@ -11274,7 +11280,7 @@
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>323</v>
+        <v>508</v>
       </c>
       <c r="N5">
         <v>1</v>
@@ -11346,7 +11352,7 @@
         <v>4</v>
       </c>
       <c r="L8" t="s">
-        <v>35</v>
+        <v>507</v>
       </c>
       <c r="N8">
         <v>4</v>
@@ -11363,12 +11369,6 @@
         <v>375</v>
       </c>
       <c r="H9">
-        <v>5</v>
-      </c>
-      <c r="L9" t="s">
-        <v>34</v>
-      </c>
-      <c r="N9">
         <v>5</v>
       </c>
     </row>

--- a/Excel/STUDI KASUS.xlsx
+++ b/Excel/STUDI KASUS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KULIAH\SEMESTER 7\PROPOSAL SKRIPSI\skripsi\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D4CF4A9-C805-4752-AA93-5C94D83DCA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948D4029-37F7-4C9B-9AB3-9059DB3A32E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="691" activeTab="3" xr2:uid="{901D0503-6946-40CA-8D36-37B156763246}"/>
   </bookViews>
@@ -12152,7 +12152,7 @@
         <v>667.66700000000003</v>
       </c>
       <c r="D52" s="104">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E52" s="36" t="s">
         <v>301</v>
@@ -12353,7 +12353,7 @@
         <v>305</v>
       </c>
       <c r="D57" s="75">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E57" s="36" t="s">
         <v>296</v>
